--- a/artfynd/A 49336-2023 artfynd.xlsx
+++ b/artfynd/A 49336-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49336-2023 artfynd.xlsx
+++ b/artfynd/A 49336-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790275</v>
+        <v>96790279</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555012.6866810267</v>
+        <v>554950</v>
       </c>
       <c r="R2" t="n">
-        <v>6953704.371566841</v>
+        <v>6953774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig, naturskogsartad  granskog</t>
+          <t>äldre granskog med torrträd</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790279</v>
+        <v>96790280</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554949.9458062798</v>
+        <v>554917</v>
       </c>
       <c r="R3" t="n">
-        <v>6953773.546005391</v>
+        <v>6953780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790278</v>
+        <v>119013554</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555002.0349079715</v>
+        <v>555162</v>
       </c>
       <c r="R4" t="n">
-        <v>6953764.317463483</v>
+        <v>6953756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,48 +984,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>olikåldrig, naturskogsartad  granskog med hänglav</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96790277</v>
+        <v>119013539</v>
       </c>
       <c r="B5" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,34 +1011,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219795</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555007.9086038761</v>
+        <v>554970</v>
       </c>
       <c r="R5" t="n">
-        <v>6953770.381845279</v>
+        <v>6953757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,22 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,62 +1081,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>vid källmiljö i olikåldrig, naturskogsartad  granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96790280</v>
+        <v>96790277</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>219795</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1223,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554916.7413034006</v>
+        <v>555008</v>
       </c>
       <c r="R6" t="n">
-        <v>6953780.336079099</v>
+        <v>6953770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,21 +1165,11 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1282,15 +1181,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>äldre granskog med torrträd</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+          <t>vid källmiljö i olikåldrig, naturskogsartad  granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1312,15 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119013524</v>
+        <v>119013556</v>
       </c>
       <c r="B7" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,21 +1214,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1352,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554888</v>
+        <v>555116</v>
       </c>
       <c r="R7" t="n">
-        <v>6953688</v>
+        <v>6953713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,50 +1300,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119013528</v>
+        <v>96790275</v>
       </c>
       <c r="B8" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555059</v>
+        <v>555012</v>
       </c>
       <c r="R8" t="n">
-        <v>6953726</v>
+        <v>6953705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,12 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,66 +1381,78 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>olikåldrig, naturskogsartad  granskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119013554</v>
+        <v>96790278</v>
       </c>
       <c r="B9" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555162</v>
+        <v>555002</v>
       </c>
       <c r="R9" t="n">
-        <v>6953756</v>
+        <v>6953764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,12 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,31 +1495,43 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>olikåldrig, naturskogsartad  granskog med hänglav</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119013565</v>
+        <v>119013564</v>
       </c>
       <c r="B10" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555098</v>
+        <v>555047</v>
       </c>
       <c r="R10" t="n">
-        <v>6953757</v>
+        <v>6953724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,7 +1607,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>300 badrosetter 3 blomställningar</t>
+          <t>300 bladrosetter, 8 blomsällningar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,50 +1635,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119013522</v>
+        <v>119013565</v>
       </c>
       <c r="B11" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554977</v>
+        <v>555098</v>
       </c>
       <c r="R11" t="n">
-        <v>6953755</v>
+        <v>6953757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,12 +1712,18 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>300 badrosetter 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,15 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119013564</v>
+        <v>119013567</v>
       </c>
       <c r="B12" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1772,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1876,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555047</v>
+        <v>555033</v>
       </c>
       <c r="R12" t="n">
-        <v>6953724</v>
+        <v>6953743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,7 +1821,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>300 bladrosetter, 8 blomsällningar</t>
+          <t>250 bladrosetter 10 blomställningar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,50 +1849,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119013534</v>
+        <v>119013568</v>
       </c>
       <c r="B13" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555079</v>
+        <v>554894</v>
       </c>
       <c r="R13" t="n">
-        <v>6953741</v>
+        <v>6953706</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,12 +1926,18 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>130 bladrosetter 10 blomställningar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2046,15 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119013572</v>
+        <v>119013569</v>
       </c>
       <c r="B14" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +1986,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2090,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555061</v>
+        <v>554892</v>
       </c>
       <c r="R14" t="n">
-        <v>6953725</v>
+        <v>6953713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2035,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 bladrosetter 3 blomställningar</t>
+          <t>55 bladrosetter 8 blomställningar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,50 +2063,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119013539</v>
+        <v>119013572</v>
       </c>
       <c r="B15" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554970</v>
+        <v>555061</v>
       </c>
       <c r="R15" t="n">
-        <v>6953757</v>
+        <v>6953725</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,12 +2140,18 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 bladrosetter 3 blomställningar</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2263,12 +2173,7 @@
         <v>119013551</v>
       </c>
       <c r="B16" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,15 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119013556</v>
+        <v>119013522</v>
       </c>
       <c r="B17" t="n">
-        <v>98210</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,21 +2278,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555116</v>
+        <v>554977</v>
       </c>
       <c r="R17" t="n">
-        <v>6953713</v>
+        <v>6953755</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,54 +2364,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119013569</v>
+        <v>119013524</v>
       </c>
       <c r="B18" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554892</v>
+        <v>554888</v>
       </c>
       <c r="R18" t="n">
-        <v>6953713</v>
+        <v>6953688</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,18 +2437,12 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>55 bladrosetter 8 blomställningar</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2576,54 +2461,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119013567</v>
+        <v>119013528</v>
       </c>
       <c r="B19" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555033</v>
+        <v>555059</v>
       </c>
       <c r="R19" t="n">
-        <v>6953743</v>
+        <v>6953726</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,18 +2534,12 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>250 bladrosetter 10 blomställningar</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2688,54 +2558,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119013568</v>
+        <v>119013534</v>
       </c>
       <c r="B20" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554894</v>
+        <v>555079</v>
       </c>
       <c r="R20" t="n">
-        <v>6953706</v>
+        <v>6953741</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2770,18 +2631,12 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>130 bladrosetter 10 blomställningar</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49336-2023 artfynd.xlsx
+++ b/artfynd/A 49336-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790279</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013554</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790277</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013556</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790275</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790278</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013565</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013567</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013568</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013569</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013572</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013551</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013522</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013524</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2555,6 +2645,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013528</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,8 +2747,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>